--- a/Control Algorithms/V1/Architecture/V1.0 Signals and Variables List.xlsx
+++ b/Control Algorithms/V1/Architecture/V1.0 Signals and Variables List.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\FB26_Controls\Control Algorithms\V1\Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3C1C98C-D3D2-4564-A15F-1404031EEFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FB7B9E-9E1E-4B73-8542-E789B705DCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{369501CE-6CA8-45C0-AE74-A62BF0386ED2}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{369501CE-6CA8-45C0-AE74-A62BF0386ED2}"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
+    <sheet name="Variables" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="93">
   <si>
     <t>Signal</t>
   </si>
@@ -93,6 +94,228 @@
   </si>
   <si>
     <t>KW</t>
+  </si>
+  <si>
+    <t>Front Master Cylinder Brake Pressure</t>
+  </si>
+  <si>
+    <t>BRK_F</t>
+  </si>
+  <si>
+    <t>Mpa</t>
+  </si>
+  <si>
+    <t>Regen Brake Torque Command</t>
+  </si>
+  <si>
+    <t>CMD_R</t>
+  </si>
+  <si>
+    <t>Nm</t>
+  </si>
+  <si>
+    <t>The regen torque commanded per wheel</t>
+  </si>
+  <si>
+    <t>RL Torque Vectoring Torque Command</t>
+  </si>
+  <si>
+    <t>RR Torque Vectoring Torque Command</t>
+  </si>
+  <si>
+    <t>RL Traction Control Torque Command</t>
+  </si>
+  <si>
+    <t>RR Traction Control Torque Command</t>
+  </si>
+  <si>
+    <t>CMD_TV_RL</t>
+  </si>
+  <si>
+    <t>CMD_TV_RR</t>
+  </si>
+  <si>
+    <t>CMD_TC_RL</t>
+  </si>
+  <si>
+    <t>CMD_TC_RR</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Regenerative Braking Torque Gain</t>
+  </si>
+  <si>
+    <t>REGEN_GAIN</t>
+  </si>
+  <si>
+    <t>Nm/MPa</t>
+  </si>
+  <si>
+    <t>A gain applied to the front master cylinder brake pressure to calculate the regen torque to apply from the rear motors</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Steering Wheel Angle</t>
+  </si>
+  <si>
+    <t>delta_SW</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
+    <t>Steering Wheel Torque Vectoring Gain</t>
+  </si>
+  <si>
+    <t>SW_TV_GAIN</t>
+  </si>
+  <si>
+    <t>Nm/deg</t>
+  </si>
+  <si>
+    <t>The torque vectoring torque difference across the rear axle applied as a result of a steering input</t>
+  </si>
+  <si>
+    <t>Throttle Pedal Position</t>
+  </si>
+  <si>
+    <t>P_T</t>
+  </si>
+  <si>
+    <t>The amount the throttle has been depressed from 0 to 1</t>
+  </si>
+  <si>
+    <t>Throttle Pedal Torque Command</t>
+  </si>
+  <si>
+    <t>CMD_T</t>
+  </si>
+  <si>
+    <t>The torque commanded by the throttle pedal</t>
+  </si>
+  <si>
+    <t>Maximum Motor Torque</t>
+  </si>
+  <si>
+    <t>Tmax</t>
+  </si>
+  <si>
+    <t>The maximum availible motor output power</t>
+  </si>
+  <si>
+    <t>Lateral Acceleration</t>
+  </si>
+  <si>
+    <t>Ay</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>RL Wheel Speed</t>
+  </si>
+  <si>
+    <t>RR Wheel Speed</t>
+  </si>
+  <si>
+    <t>omega_RL</t>
+  </si>
+  <si>
+    <t>omega_RR</t>
+  </si>
+  <si>
+    <t>rpm</t>
+  </si>
+  <si>
+    <t>Degrees to Radians Conversion</t>
+  </si>
+  <si>
+    <t>deg_to_rad</t>
+  </si>
+  <si>
+    <t>rad/deg</t>
+  </si>
+  <si>
+    <t>RL Motor Torque Command</t>
+  </si>
+  <si>
+    <t>RR Motor Torque Command</t>
+  </si>
+  <si>
+    <t>CMD_RR</t>
+  </si>
+  <si>
+    <t>CMD_RL</t>
+  </si>
+  <si>
+    <t>Torque command sent to the RL motor</t>
+  </si>
+  <si>
+    <t>Torque command sent to the RR motor</t>
+  </si>
+  <si>
+    <t>omega_FL</t>
+  </si>
+  <si>
+    <t>FL Wheel Speed</t>
+  </si>
+  <si>
+    <t>FR Wheel Speed</t>
+  </si>
+  <si>
+    <t>omega_FR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitudinal Acceleration </t>
+  </si>
+  <si>
+    <t>Ax</t>
+  </si>
+  <si>
+    <t>RL Wheel Slip Ratio</t>
+  </si>
+  <si>
+    <t>RR Wheel Slip Ratio</t>
+  </si>
+  <si>
+    <t>kappa_RL</t>
+  </si>
+  <si>
+    <t>kappa_RR</t>
+  </si>
+  <si>
+    <t>Effective Tire Radius</t>
+  </si>
+  <si>
+    <t>R_e</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>The radius of the tire from the wheel center to the contact patch</t>
+  </si>
+  <si>
+    <t>Slip Ratio Threshold</t>
+  </si>
+  <si>
+    <t>kappa_thresh</t>
+  </si>
+  <si>
+    <t>The threshold at which the TC will begin to engage for slip ratio</t>
+  </si>
+  <si>
+    <t>Traction Control Cut Gain</t>
+  </si>
+  <si>
+    <t>TC_CUT</t>
+  </si>
+  <si>
+    <t>The percent of power the traction control cuts by</t>
   </si>
 </sst>
 </file>
@@ -473,10 +696,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A8C4BDE-4690-4971-B306-A3FB87DFB891}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="60.7109375" bestFit="1" customWidth="1"/>
@@ -552,6 +775,398 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E40D3DF-DFC2-4EE4-8BC8-226388D2D6FF}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="105.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5">
+        <v>1.7453300000000001E-2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>0.12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
